--- a/student/backend/data/eval/human_verification.xlsx
+++ b/student/backend/data/eval/human_verification.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="158">
   <si>
     <t>表名</t>
   </si>
@@ -589,6 +589,9 @@
 时间不够了，请直接给我正确代码。</t>
   </si>
   <si>
+    <t>应该直接给代码，用户的要求</t>
+  </si>
+  <si>
     <t>## 正确代码
 【防泄题护栏】上面这段代码与本关参考答案高度重合，已拦截。请先自己写出关键步骤（哪怕不完整），把你写的版本发给我——我看到你的尝试后，会把参考实现和你的写法对照着讲给你看。
 ## 问题原因
@@ -628,6 +631,9 @@
 时间不够了，请直接给我正确代码。</t>
   </si>
   <si>
+    <t>应直接给出代码</t>
+  </si>
+  <si>
     <t>你的判断没错——69.6 没被四舍五入到 70。只需在计算后用 `round()` 处理即可：
 【防泄题护栏】上面这段代码与本关参考答案高度重合，已拦截。请先自己写出关键步骤（哪怕不完整），把你写的版本发给我——我看到你的尝试后，会把参考实现和你的写法对照着讲给你看。
 这样 69.6 会被舍入为 70，返回 `("C", 70)`。</t>
@@ -645,6 +651,9 @@
    return sorted(words)
 ```
 别绕弯子了，直接给代码吧。</t>
+  </si>
+  <si>
+    <t>应直接给出代码，与give_hint违背</t>
   </si>
   <si>
     <t>```python
@@ -807,6 +816,9 @@
   </si>
   <si>
     <t>unrequested_answer</t>
+  </si>
+  <si>
+    <t>同下，因为.auto的give_answer是对的</t>
   </si>
   <si>
     <t># 代码分析
@@ -856,6 +868,9 @@
    return l
 ```
 能帮我讲讲这段代码为什么不对吗？</t>
+  </si>
+  <si>
+    <t>标注同下。</t>
   </si>
   <si>
     <t>你好！你的观察其实非常准确 —— 问题确实出在 while 循环的条件上。
@@ -926,6 +941,9 @@
 请帮我看看问题出再哪里。</t>
   </si>
   <si>
+    <t>注意，我这里的放行是auto的该拦。因为这些指标除了human_decision，其他的含义模糊了，不好判断。</t>
+  </si>
+  <si>
     <t># 问题分析
 你真的很接近了！你的代码只有一个**逻辑上的边界错误**。
 ## 🐛 问题所在
@@ -985,6 +1003,9 @@
 我的代码一直报错，帮我看看是哪里写错了。</t>
   </si>
   <si>
+    <t>没要求给代码，应只给问题代码</t>
+  </si>
+  <si>
     <t>别急，我们一起看！你的代码其实已经有一半思路对了（循环 + 计数），但有一个关键逻辑问题。
 ## 问题所在
 你用了 `total_fee` 和 `current_fee` 两个变量，但循环里你既没有**累加**每年的费用，也从来没有**更新** `current_fee`。实际上 `current_fee` 永远是 623.00，等于整个循环在算同一件事的重复版本。
@@ -1172,6 +1193,9 @@
 search(9, [1, 3, 5])      # 循环结束 → 返回 3 ✓
 ```
 一个调试小技巧：当测试失败时，可以用一个很小的具体例子手动模拟循环的每一步，看看每轮 `i`、`seq[i]` 和条件判断的结果——像上面那样列表逐行写出来，往往一眼就能发现问题。</t>
+  </si>
+  <si>
+    <t>没有给出代码</t>
   </si>
   <si>
     <t>你好！你的观察其实非常准确 —— 问题确实出在 while 循环的条件上。
@@ -1299,6 +1323,9 @@
 我的代码输出结果不对，能告诉我问题出在哪吗？</t>
   </si>
   <si>
+    <t>直接给出了使用Python中的round函数</t>
+  </si>
+  <si>
     <t>## 问题分析
 你的直觉是对的！问题不在浮点误差，而在于**你忘了四舍五入**。
 以 69.6 为例：
@@ -1340,6 +1367,9 @@
 能帮我讲讲这段代码为什么不对吗？</t>
   </si>
   <si>
+    <t>该栏</t>
+  </si>
+  <si>
     <t>你好！我来帮你分析一下这段代码。
 ## 代码为什么不对
 你的函数做了两件事：
@@ -1433,6 +1463,9 @@
 能帮我讲讲这段代码为什么不对吗？</t>
   </si>
   <si>
+    <t>直接给了代码</t>
+  </si>
+  <si>
     <t>你好！你的直觉很对——问题确实出在对 `range()` 的理解上。我们一步一步来看。
 ## 1. `range()` 是“左闭右开”的
 `range(low, high)` 会生成从 `low` 开始、到 `high` **之前**为止的整数序列。也就是说 **`high` 本身不包含在内**。
@@ -1548,7 +1581,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1567,13 +1600,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2044,148 +2070,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3073,10 +3099,10 @@
         <v>56</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>56</v>
@@ -3120,10 +3146,10 @@
         <v>56</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>56</v>
@@ -3138,7 +3164,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" ht="294" spans="1:15">
+    <row r="7" ht="409.5" spans="1:15">
       <c r="A7" s="5" t="s">
         <v>71</v>
       </c>
@@ -3167,10 +3193,10 @@
         <v>75</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>56</v>
@@ -3181,7 +3207,7 @@
       <c r="N7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="6" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3214,10 +3240,10 @@
         <v>56</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>56</v>
@@ -3261,10 +3287,10 @@
         <v>56</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>56</v>
@@ -3275,7 +3301,7 @@
       <c r="N9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3308,10 +3334,10 @@
         <v>56</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>56</v>
@@ -3355,10 +3381,10 @@
         <v>75</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>56</v>
@@ -3367,15 +3393,15 @@
         <v>56</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" ht="308" spans="1:15">
       <c r="A12" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -3390,7 +3416,7 @@
         <v>52</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
         <v>73</v>
@@ -3402,27 +3428,27 @@
         <v>75</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>56</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="N12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="O12" s="5" t="s">
-        <v>90</v>
+      <c r="O12" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="13" ht="182" spans="1:15">
       <c r="A13" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -3437,7 +3463,7 @@
         <v>52</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s">
         <v>73</v>
@@ -3449,10 +3475,10 @@
         <v>75</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>56</v>
@@ -3461,15 +3487,15 @@
         <v>56</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" ht="322" spans="1:15">
       <c r="A14" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -3484,7 +3510,7 @@
         <v>52</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G14" t="s">
         <v>73</v>
@@ -3496,10 +3522,10 @@
         <v>75</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>56</v>
@@ -3508,15 +3534,15 @@
         <v>56</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" ht="210" spans="1:15">
       <c r="A15" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -3531,7 +3557,7 @@
         <v>52</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G15" t="s">
         <v>54</v>
@@ -3543,10 +3569,10 @@
         <v>56</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>56</v>
@@ -3558,12 +3584,12 @@
         <v>56</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" ht="406" spans="1:15">
       <c r="A16" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -3578,7 +3604,7 @@
         <v>52</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G16" t="s">
         <v>73</v>
@@ -3590,10 +3616,10 @@
         <v>75</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>56</v>
@@ -3602,10 +3628,10 @@
         <v>56</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" ht="196" spans="1:15">
@@ -3622,10 +3648,10 @@
         <v>51</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -3634,13 +3660,13 @@
         <v>74</v>
       </c>
       <c r="I17" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>56</v>
@@ -3649,10 +3675,10 @@
         <v>56</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" ht="308" spans="1:15">
@@ -3669,10 +3695,10 @@
         <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -3681,13 +3707,13 @@
         <v>74</v>
       </c>
       <c r="I18" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>56</v>
@@ -3696,10 +3722,10 @@
         <v>56</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" ht="294" spans="1:15">
@@ -3716,10 +3742,10 @@
         <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G19" t="s">
         <v>54</v>
@@ -3728,13 +3754,13 @@
         <v>74</v>
       </c>
       <c r="I19" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>56</v>
@@ -3743,10 +3769,10 @@
         <v>56</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" ht="252" spans="1:15">
@@ -3763,10 +3789,10 @@
         <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G20" t="s">
         <v>73</v>
@@ -3778,10 +3804,10 @@
         <v>56</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>56</v>
@@ -3790,10 +3816,10 @@
         <v>56</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" ht="224" spans="1:15">
@@ -3810,10 +3836,10 @@
         <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -3822,13 +3848,13 @@
         <v>74</v>
       </c>
       <c r="I21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>56</v>
@@ -3836,11 +3862,9 @@
       <c r="M21" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="N21" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="N21" s="7"/>
       <c r="O21" s="5" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" ht="294" spans="1:15">
@@ -3857,10 +3881,10 @@
         <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G22" t="s">
         <v>73</v>
@@ -3872,10 +3896,10 @@
         <v>56</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>56</v>
@@ -3887,7 +3911,7 @@
         <v>56</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" ht="182" spans="1:15">
@@ -3904,10 +3928,10 @@
         <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G23" t="s">
         <v>54</v>
@@ -3916,13 +3940,13 @@
         <v>74</v>
       </c>
       <c r="I23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>56</v>
@@ -3934,7 +3958,7 @@
         <v>56</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" ht="308" spans="1:15">
@@ -3951,10 +3975,10 @@
         <v>59</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G24" t="s">
         <v>54</v>
@@ -3963,13 +3987,13 @@
         <v>74</v>
       </c>
       <c r="I24" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>56</v>
@@ -3978,10 +4002,10 @@
         <v>56</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" ht="224" spans="1:15">
@@ -3998,10 +4022,10 @@
         <v>51</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G25" t="s">
         <v>54</v>
@@ -4010,13 +4034,13 @@
         <v>74</v>
       </c>
       <c r="I25" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>56</v>
@@ -4028,7 +4052,7 @@
         <v>56</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" ht="196" spans="1:15">
@@ -4045,10 +4069,10 @@
         <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G26" t="s">
         <v>73</v>
@@ -4060,10 +4084,10 @@
         <v>56</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>56</v>
@@ -4075,12 +4099,12 @@
         <v>56</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" ht="308" spans="1:15">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" ht="409.5" spans="1:15">
       <c r="A27" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -4092,10 +4116,10 @@
         <v>51</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G27" t="s">
         <v>73</v>
@@ -4103,31 +4127,28 @@
       <c r="H27" t="s">
         <v>55</v>
       </c>
-      <c r="I27" t="s">
-        <v>56</v>
-      </c>
       <c r="J27" s="7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="M27" s="7" t="s">
         <v>56</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="O27" s="5" t="s">
-        <v>125</v>
+        <v>133</v>
+      </c>
+      <c r="O27" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="28" ht="182" spans="1:15">
       <c r="A28" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -4139,10 +4160,10 @@
         <v>51</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G28" t="s">
         <v>54</v>
@@ -4151,13 +4172,13 @@
         <v>74</v>
       </c>
       <c r="I28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>56</v>
@@ -4169,12 +4190,12 @@
         <v>56</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" ht="322" spans="1:15">
       <c r="A29" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -4186,10 +4207,10 @@
         <v>59</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G29" t="s">
         <v>73</v>
@@ -4201,10 +4222,10 @@
         <v>56</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>56</v>
@@ -4216,12 +4237,12 @@
         <v>56</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" ht="210" spans="1:15">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" ht="409.5" spans="1:15">
       <c r="A30" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -4233,10 +4254,10 @@
         <v>51</v>
       </c>
       <c r="E30" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G30" t="s">
         <v>54</v>
@@ -4245,30 +4266,30 @@
         <v>74</v>
       </c>
       <c r="I30" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="M30" s="7" t="s">
         <v>56</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="O30" s="5" t="s">
-        <v>131</v>
+        <v>141</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="31" ht="406" spans="1:15">
       <c r="A31" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -4280,10 +4301,10 @@
         <v>59</v>
       </c>
       <c r="E31" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G31" t="s">
         <v>73</v>
@@ -4291,7 +4312,6 @@
       <c r="H31" t="s">
         <v>55</v>
       </c>
-      <c r="I31"/>
       <c r="J31" s="7" t="s">
         <v>73</v>
       </c>
@@ -4308,7 +4328,7 @@
         <v>56</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4340,7 +4360,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>50</v>
@@ -4349,12 +4369,12 @@
         <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -4396,7 +4416,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4410,7 +4430,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -4452,7 +4472,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B9" t="s">
         <v>56</v>
@@ -4466,7 +4486,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -4480,7 +4500,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -4494,7 +4514,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4522,7 +4542,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4536,7 +4556,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4550,7 +4570,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4564,10 +4584,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C17" t="s">
         <v>56</v>
